--- a/data/trans_orig/IP22D1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP22D1_2023-Provincia-trans_orig.xlsx
@@ -1108,7 +1108,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13448</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,97%</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8789</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>20741</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4816</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2991,7 +2991,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>48216</t>
+          <t>48424</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>96452</t>
+          <t>96686</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP22D1_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP22D1_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13524</t>
+          <t>8172</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23006</t>
+          <t>15607</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7537</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5372</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7946</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>67,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7602</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7763</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8178</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6195</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8701</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>93,99%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>15779</t>
+          <t>15299</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13210</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>409</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2506</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>28,8%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>3092</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>7763</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16302</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,64 +1406,64 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3312</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3529</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3467</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3312</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5909</t>
+          <t>8039</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14209</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,64 +2092,64 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1631</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1679</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>520</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>520</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>520</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4070</t>
+          <t>3145</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>6645</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11787</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8019</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>12731</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>92,59%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>62,99%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>11175</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>11526</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>12680</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>8758</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>13605</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>93,2%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,27 +2853,27 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>23855</t>
+          <t>23314</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20741</t>
+          <t>19617</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,107 +2891,107 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>944</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>4847</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>6,8%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>4641</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>35,62%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>4039</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11175</t>
+          <t>12731</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24258</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>3510</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3159</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>47147</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>43052</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>88,77%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>43031</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>51824</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>48424</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>53272</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,27 +3539,27 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>99990</t>
+          <t>90178</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>96686</t>
+          <t>86312</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3577,107 +3577,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>4848</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1448</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>4752</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>48500</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>48166</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53272</t>
+          <t>43031</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>101438</t>
+          <t>91531</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
